--- a/data/jd_database.xlsx
+++ b/data/jd_database.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,6 +868,110 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Testing D</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning, Generative AI, Large Language Models (LLMs), Agentic AI, Conversational AI, Digital Transformation, Enterprise Technology Strategy, Business Consulting, AI Model Governance, Ethics in AI, Security Frameworks, Cloud Platforms, Google Cloud, Vertex AI, Cross-functional Team Leadership, Stakeholder Communication, Executive Advisory, Innovation Insights, BFSI Domain Knowledge, Enterprise-scale Digital Transformation, Technology Roadmaps, AI/ML Engineering, AI Architecture, Master's Degree, M.Tech, MBA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning, Generative AI, Large Language Models (LLMs), Cloud Computing, Google Cloud, Vertex AI, Digital Transformation, AI Governance, BFSI, AI Strategy, Cross-functional Leadership, Executive Consulting</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>"Artificial Intelligence" AND "Machine Learning" AND "Generative AI" AND "Large Language Models (LLMs)" AND "Cloud Computing" AND "Google Cloud" AND "Vertex AI" AND "Digital Transformation"</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Executive Level</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lead AI strategy including Generative AI, LLMs, Agentic AI, Conversational AI. | Drive digital transformation aligned with business goals. | Establish AI model governance, ethics, and security frameworks. | Collaborate with CXOs to define technology and innovation roadmaps. | Oversee deployment of AI solutions using platforms like Google Cloud, Vertex AI. | Lead cross-functional AI/ML engineering and architecture teams. | Provide executive-level advisory, consulting, and innovation insights.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Master’s degree required (M.Tech / MBA preferred)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>marketscope</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Testing E</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UI/UX Design, User-Centered Design Principles, User Research, Competitive Analysis, Usability Testing, Wireframing, User Flows, Mockups, Interactive Prototypes, Collaboration with Product Managers, Collaboration with Developers, Design Systems, User Feedback Iteration, Accessibility Best Practices, Proficiency in Figma, Proficiency in Adobe XD, Proficiency in Sketch, UX Principles, Human-Computer Interaction (HCI), Visual Design Fundamentals, Responsive Design, Mobile-First Design, Persona Development, Journey Mapping, Front-End Basics (HTML, CSS), AI-Driven Prototyping Tools, Creative Problem-Solving, Attention to Detail, Collaboration Skills, Communication Skills, User Empathy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>UI/UX Design, Figma, Adobe XD, Sketch, Usability Testing, Responsive Design, Human-Computer Interaction (HCI), Wireframing, User Flows, Mockups, Interactive Prototypes, Design Systems, User-Centered Design Principles, Visual Design Fundamentals</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>"UI/UX Design" AND "Figma" AND "Adobe XD" AND "Sketch" AND "Usability Testing" AND "Responsive Design" AND "Human-Computer Interaction (HCI)" AND "Wireframing"</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Conduct user research, competitive analysis, and usability testing. | Create wireframes, user flows, mockups, and interactive prototypes. | Collaborate with product managers and developers to translate concepts into user experiences. | Develop and maintain scalable design systems. | Iterate based on user feedback and testing insights. | Ensure alignment with accessibility and UI best practices.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Design | Bachelor's degree in HCI | Bachelor's degree in related field</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>marketscope</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/jd_database.xlsx
+++ b/data/jd_database.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,58 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Testing B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sales, Enterprise Software Solutions, Banking Industry Knowledge, Insurance Industry Knowledge, Business Process Management (BPM), Enterprise Content Management (ECM), Case Management, Low-Code Development, Hyper-Automation Applications, Consultative Selling, Account Planning, Account Management, Lead Generation Strategies, Customer Relationship Management, Cross-Department Collaboration, Market Traction Generation, Strategic Target Account Planning, Sales Cycle Management, Customer Satisfaction, Face-to-Face Customer Interactions, Sales Quota Achievement, Multicultural Team Collaboration, Networking with System Integrators, Travel for Business, Bachelor's Degree</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Enterprise Software Solutions, Business Process Management (BPM), Enterprise Content Management (ECM), Case Management, Low-Code Development, Hyper-Automation Applications, Consultative Selling, Account Management, Lead Generation Strategies, Sales Cycle Management, Banking Industry Knowledge, Insurance Industry Knowledge</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>"Enterprise Software Solutions" AND "Business Process Management (BPM)" AND "Enterprise Content Management (ECM)" AND "Case Management" AND "Low-Code Development" AND "Hyper-Automation Applications" AND "Consultative Selling" AND "Account Management"</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Senior Level</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Meet and exceed assigned revenue targets on quarterly basis | Oversee the Billing/ Contracting/ Collection of Payment from the customer | Create detailed, strategic target account plans | Think and research strategically about client’s business | Leverage Newgen resources to identify and drive sales campaigns | Effectively manage a complex sales cycle to a successful close</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>marketscope</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
